--- a/Seminar 2/MREZA_CESTOVNIH_PRAVACA_CUSTOM.xlsx
+++ b/Seminar 2/MREZA_CESTOVNIH_PRAVACA_CUSTOM.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CFDC75E-06FA-4FB5-941A-169828A5D422}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{799F1687-4755-47D6-B9FF-4E443D388B74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MREŽA CESTOVNIH PRAVACA" sheetId="3" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="81">
   <si>
     <t>POLAZIŠTE</t>
   </si>
@@ -37,9 +37,6 @@
     <t>D2</t>
   </si>
   <si>
-    <t>D43</t>
-  </si>
-  <si>
     <t>TRAJANJE [min]</t>
   </si>
   <si>
@@ -212,9 +209,6 @@
   </si>
   <si>
     <t>Okučani</t>
-  </si>
-  <si>
-    <t>Čazma</t>
   </si>
   <si>
     <t>Slatina</t>
@@ -627,7 +621,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92A7DD6A-5C38-4119-AE6E-7E25FE5531AA}">
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr defaultColWidth="15.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -649,21 +643,21 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="C2" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>10</v>
       </c>
       <c r="D2" s="5">
         <v>53.3</v>
@@ -677,13 +671,13 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D3" s="5">
         <v>57.5</v>
@@ -697,13 +691,13 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>13</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>14</v>
       </c>
       <c r="D4" s="5">
         <v>87</v>
@@ -717,13 +711,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D5" s="5">
         <v>18.7</v>
@@ -737,13 +731,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>15</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>16</v>
       </c>
       <c r="D6" s="5">
         <v>114</v>
@@ -757,13 +751,13 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>10</v>
       </c>
       <c r="D7" s="5">
         <v>152</v>
@@ -777,13 +771,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>10</v>
       </c>
       <c r="D8" s="5">
         <v>57.2</v>
@@ -797,13 +791,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D9" s="5">
         <v>13.7</v>
@@ -817,13 +811,13 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D10" s="5">
         <v>43.4</v>
@@ -837,13 +831,13 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B11" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>21</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>22</v>
       </c>
       <c r="D11" s="5">
         <v>14.9</v>
@@ -857,10 +851,10 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>4</v>
@@ -877,13 +871,13 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D13" s="5">
         <v>108</v>
@@ -897,13 +891,13 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B14" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>26</v>
       </c>
       <c r="D14" s="5">
         <v>13.7</v>
@@ -917,13 +911,13 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D15" s="5">
         <v>99.3</v>
@@ -937,13 +931,13 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D16" s="5">
         <v>221</v>
@@ -957,13 +951,13 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D17" s="5">
         <v>21.4</v>
@@ -977,13 +971,13 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D18" s="5">
         <v>34</v>
@@ -997,13 +991,13 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D19" s="5">
         <v>16.5</v>
@@ -1017,13 +1011,13 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D20" s="5">
         <v>32.4</v>
@@ -1037,10 +1031,10 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>4</v>
@@ -1057,13 +1051,13 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B22" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" s="4" t="s">
         <v>33</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="D22" s="5">
         <v>36.1</v>
@@ -1077,13 +1071,13 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B23" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C23" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>42</v>
       </c>
       <c r="D23" s="5">
         <v>43.8</v>
@@ -1097,13 +1091,13 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D24" s="5">
         <v>88.4</v>
@@ -1117,13 +1111,13 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D25" s="5">
         <v>29.4</v>
@@ -1137,13 +1131,13 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D26" s="5">
         <v>84.8</v>
@@ -1157,13 +1151,13 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D27" s="5">
         <v>232.5</v>
@@ -1177,13 +1171,13 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D28" s="5">
         <v>27.3</v>
@@ -1197,13 +1191,13 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D29" s="5">
         <v>34.200000000000003</v>
@@ -1217,13 +1211,13 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D30" s="5">
         <v>43.8</v>
@@ -1237,13 +1231,13 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D31" s="5">
         <v>71.5</v>
@@ -1257,13 +1251,13 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D32" s="5">
         <v>84.7</v>
@@ -1277,13 +1271,13 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D33" s="5">
         <v>70.5</v>
@@ -1297,13 +1291,13 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B34" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C34" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>50</v>
       </c>
       <c r="D34" s="5">
         <v>48.9</v>
@@ -1317,13 +1311,13 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D35" s="5">
         <v>31.3</v>
@@ -1337,13 +1331,13 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D36" s="5">
         <v>31.8</v>
@@ -1357,10 +1351,10 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>4</v>
@@ -1377,13 +1371,13 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D38" s="5">
         <v>36.200000000000003</v>
@@ -1397,13 +1391,13 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C39" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>42</v>
       </c>
       <c r="D39" s="5">
         <v>4.7</v>
@@ -1417,13 +1411,13 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B40" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C40" s="4" t="s">
         <v>56</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>57</v>
       </c>
       <c r="D40" s="5">
         <v>56.1</v>
@@ -1437,13 +1431,13 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D41" s="5">
         <v>7.7</v>
@@ -1457,13 +1451,13 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D42" s="5">
         <v>36.700000000000003</v>
@@ -1477,13 +1471,13 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D43" s="5">
         <v>55.2</v>
@@ -1497,13 +1491,13 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D44" s="5">
         <v>25.2</v>
@@ -1517,13 +1511,13 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D45" s="5">
         <v>64</v>
@@ -1537,13 +1531,13 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D46" s="5">
         <v>3.4</v>
@@ -1557,13 +1551,13 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D47" s="5">
         <v>23.9</v>
@@ -1577,13 +1571,13 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D48" s="5">
         <v>22</v>
@@ -1597,10 +1591,10 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>4</v>
@@ -1620,38 +1614,18 @@
         <v>52</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D50" s="5">
-        <v>30.6</v>
+        <v>30.1</v>
       </c>
       <c r="E50" s="2">
         <v>65</v>
       </c>
       <c r="F50" s="2">
-        <v>28.2</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="D51" s="5">
-        <v>30.1</v>
-      </c>
-      <c r="E51" s="2">
-        <v>65</v>
-      </c>
-      <c r="F51" s="2">
         <v>27.8</v>
       </c>
     </row>
